--- a/data/trans_dic/P55$auxiliar-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P55$auxiliar-Edad-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,98%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,4</t>
+          <t>0,0; 10,25</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,76</t>
+          <t>0,0; 14,07</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,38</t>
+          <t>0,0; 15,41</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,44; 13,86</t>
+          <t>2,21; 12,79</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,0</t>
+          <t>0,0; 8,33</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,88; 16,12</t>
+          <t>4,02; 17,86</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,4</t>
+          <t>0,0; 11,46</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8,37; 20,02</t>
+          <t>9,34; 21,66</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,76; 6,79</t>
+          <t>0,75; 6,61</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3,26; 12,58</t>
+          <t>3,31; 12,38</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,85; 9,86</t>
+          <t>0,85; 8,56</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>7,03; 15,16</t>
+          <t>7,51; 15,48</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>27,25%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>26,6%</t>
+          <t>26,28%</t>
         </is>
       </c>
     </row>
@@ -862,57 +862,57 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,45; 16,51</t>
+          <t>4,31; 17,15</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,86; 11,02</t>
+          <t>1,82; 10,82</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17,72; 30,53</t>
+          <t>17,73; 31,54</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,04; 9,63</t>
+          <t>2,06; 9,96</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,32; 28,04</t>
+          <t>15,91; 27,76</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,22; 12,99</t>
+          <t>4,44; 13,2</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>24,43; 32,36</t>
+          <t>23,26; 31,36</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,32; 5,91</t>
+          <t>1,35; 5,84</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13,69; 22,39</t>
+          <t>13,96; 22,57</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4,42; 11,1</t>
+          <t>4,41; 10,94</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>23,58; 29,83</t>
+          <t>23,17; 29,89</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>24,31%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>22,34%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,59</t>
+          <t>0,0; 3,37</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,21; 13,99</t>
+          <t>4,38; 13,59</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,01; 9,49</t>
+          <t>2,0; 9,63</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>14,04; 24,15</t>
+          <t>13,71; 23,67</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,91; 7,67</t>
+          <t>1,99; 7,38</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>14,12; 23,98</t>
+          <t>14,1; 23,8</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,81; 10,86</t>
+          <t>3,71; 10,81</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>21,19; 28,1</t>
+          <t>21,33; 27,47</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,51; 5,32</t>
+          <t>1,31; 5,09</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>11,57; 18,56</t>
+          <t>11,78; 19,01</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3,7; 8,66</t>
+          <t>3,81; 9,16</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>19,87; 25,45</t>
+          <t>19,87; 25,28</t>
         </is>
       </c>
     </row>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3375</t>
+          <t>3452</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>9663</t>
+          <t>11428</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1350,7 +1350,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>13038</t>
+          <t>14880</t>
         </is>
       </c>
     </row>
@@ -1363,62 +1363,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 3511</t>
+          <t>0; 4284</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 7164</t>
+          <t>0; 6395</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 5134</t>
+          <t>0; 4831</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1229; 6989</t>
+          <t>1215; 7043</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 6769</t>
+          <t>0; 5633</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2008; 11237</t>
+          <t>2804; 12451</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 9365</t>
+          <t>0; 9410</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>6116; 14618</t>
+          <t>7519; 17442</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>834; 7434</t>
+          <t>826; 7239</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3753; 14484</t>
+          <t>3808; 14254</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>968; 11184</t>
+          <t>962; 9718</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>8679; 18709</t>
+          <t>10179; 20991</t>
         </is>
       </c>
     </row>
@@ -1518,7 +1518,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>25173</t>
+          <t>27284</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1538,7 +1538,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>71089</t>
+          <t>75419</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1558,7 +1558,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>96261</t>
+          <t>102703</t>
         </is>
       </c>
     </row>
@@ -1576,57 +1576,57 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4482; 16633</t>
+          <t>4344; 17271</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1673; 9934</t>
+          <t>1639; 9753</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>18901; 32567</t>
+          <t>20222; 35969</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3337; 15730</t>
+          <t>3365; 16258</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>34249; 58833</t>
+          <t>33379; 58255</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7810; 24066</t>
+          <t>8225; 24441</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>62349; 82588</t>
+          <t>64379; 86786</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3270; 14660</t>
+          <t>3342; 14487</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>42501; 69512</t>
+          <t>43354; 70074</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>12180; 30572</t>
+          <t>12141; 30111</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>85326; 107957</t>
+          <t>90532; 116795</t>
         </is>
       </c>
     </row>
@@ -1726,7 +1726,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>28548</t>
+          <t>30736</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>80752</t>
+          <t>86848</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>109300</t>
+          <t>117584</t>
         </is>
       </c>
     </row>
@@ -1779,62 +1779,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 4547</t>
+          <t>0; 4266</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6158; 20445</t>
+          <t>6405; 19858</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2442; 11524</t>
+          <t>2430; 11702</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>22056; 37927</t>
+          <t>23183; 40028</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>4420; 17722</t>
+          <t>4599; 17041</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>39457; 67023</t>
+          <t>39427; 66518</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10177; 29027</t>
+          <t>9908; 28902</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>69568; 92229</t>
+          <t>76206; 98127</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>5392; 19014</t>
+          <t>4675; 18213</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>49252; 79016</t>
+          <t>50132; 80908</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>14368; 33654</t>
+          <t>14812; 35603</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>96424; 123491</t>
+          <t>104581; 133084</t>
         </is>
       </c>
     </row>
